--- a/data/trans_orig/P04A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023</t>
+          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61177</t>
+          <t>61754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45965</t>
+          <t>45099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66107</t>
+          <t>66437</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101717</t>
+          <t>99670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25342</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133676</t>
+          <t>132372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176659</t>
+          <t>177139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128048</t>
+          <t>126160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160633</t>
+          <t>161022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267966</t>
+          <t>269941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325245</t>
+          <t>329052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>253737</t>
+          <t>253458</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>298602</t>
+          <t>297994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>225474</t>
+          <t>226099</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>261776</t>
+          <t>262845</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>490541</t>
+          <t>490295</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>551339</t>
+          <t>551302</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>31329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60231</t>
+          <t>59353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27806</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>49537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67114</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102532</t>
+          <t>102741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>24733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35474</t>
+          <t>34324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>129167</t>
+          <t>127359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170593</t>
+          <t>171116</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,47 +1992,47 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>38,02%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>144355</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>127699</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>161374</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>37,9%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>144355</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>128362</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>160605</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>267583</t>
+          <t>269678</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>321447</t>
+          <t>322007</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>219947</t>
+          <t>221142</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>263094</t>
+          <t>265579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160076</t>
+          <t>160645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193287</t>
+          <t>194271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>391006</t>
+          <t>390269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>445516</t>
+          <t>446918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74975</t>
+          <t>75696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80810</t>
+          <t>81178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>52703</t>
+          <t>52463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169234</t>
+          <t>170413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50420</t>
+          <t>49056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>58067</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207698</t>
+          <t>210907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>377018</t>
+          <t>374792</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599183</t>
+          <t>596928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96447</t>
+          <t>97075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116216</t>
+          <t>116546</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487299</t>
+          <t>485584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>736065</t>
+          <t>737575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41514</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25760</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>26396</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58111</t>
+          <t>59865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91581</t>
+          <t>89480</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>151118</t>
+          <t>147082</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39674</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>110892</t>
+          <t>111574</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>135970</t>
+          <t>140645</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>240016</t>
+          <t>241251</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>42414</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>81816</t>
+          <t>80227</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>52854</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64250</t>
+          <t>66047</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>123503</t>
+          <t>121083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>214104</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>275300</t>
+          <t>272313</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110990</t>
+          <t>121926</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>297539</t>
+          <t>298101</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>319451</t>
+          <t>329814</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>537565</t>
+          <t>537833</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>544921</t>
+          <t>545895</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>621853</t>
+          <t>621181</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>499177</t>
+          <t>493938</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>799297</t>
+          <t>780801</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1077809</t>
+          <t>1078121</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1449472</t>
+          <t>1461740</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31251</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>18925</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>42593</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48304</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>76844</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>89001</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>330460</t>
+          <t>342288</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>148066</t>
+          <t>150909</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>419788</t>
+          <t>402756</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>57449</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>51843</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>63125</t>
+          <t>62245</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>102965</t>
+          <t>103488</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>73505</t>
+          <t>72472</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>113554</t>
+          <t>114621</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>114881</t>
+          <t>112507</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>181149</t>
+          <t>177441</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>199196</t>
+          <t>198279</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>278668</t>
+          <t>278120</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>230037</t>
+          <t>227204</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>275527</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>345554</t>
+          <t>351082</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>529331</t>
+          <t>530039</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>614160</t>
+          <t>599028</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>791481</t>
+          <t>783283</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18834</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>87224</t>
+          <t>87597</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>61453</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>106368</t>
+          <t>107397</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37762</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54105</t>
+          <t>52703</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>37824</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>84225</t>
+          <t>81869</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>95642</t>
+          <t>95227</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>138932</t>
+          <t>135852</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>141590</t>
+          <t>143907</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>208800</t>
+          <t>205016</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>102360</t>
+          <t>103800</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>152569</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>517299</t>
+          <t>516820</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>571877</t>
+          <t>569173</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>636641</t>
+          <t>639138</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>710573</t>
+          <t>709455</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>53586</t>
+          <t>55903</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>36187</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>78504</t>
+          <t>78124</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>39832</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>75771</t>
+          <t>76902</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>83471</t>
+          <t>84330</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>129138</t>
+          <t>131403</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>252064</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>375245</t>
+          <t>375562</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>307378</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>606324</t>
+          <t>592783</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>621418</t>
+          <t>615623</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>944525</t>
+          <t>957653</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>130781</t>
+          <t>130966</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>209626</t>
+          <t>208490</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>103585</t>
+          <t>103793</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>153264</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>254245</t>
+          <t>255530</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>348308</t>
+          <t>346268</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>615692</t>
+          <t>626977</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>879429</t>
+          <t>888551</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>665191</t>
+          <t>661904</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>894148</t>
+          <t>894477</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1378215</t>
+          <t>1397664</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1751797</t>
+          <t>1744860</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1842215</t>
+          <t>1839584</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2278478</t>
+          <t>2291789</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2021394</t>
+          <t>2008238</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2419278</t>
+          <t>2384177</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3895948</t>
+          <t>3915515</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4489088</t>
+          <t>4479297</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47177</t>
+          <t>65414</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>48440</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61754</t>
+          <t>81902</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34504</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25191</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>60042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>81681</t>
+          <t>111727</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66437</t>
+          <t>93563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99670</t>
+          <t>131873</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25752</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>33780</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>47835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>153607</t>
+          <t>157255</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132372</t>
+          <t>135863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177139</t>
+          <t>182477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>143509</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126160</t>
+          <t>133475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161022</t>
+          <t>170334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>297116</t>
+          <t>308596</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269941</t>
+          <t>281037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329052</t>
+          <t>341948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>275647</t>
+          <t>299614</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>253458</t>
+          <t>274631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>297994</t>
+          <t>323541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>245350</t>
+          <t>266950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>226099</t>
+          <t>247707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>262845</t>
+          <t>284950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>520997</t>
+          <t>566564</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>490295</t>
+          <t>535368</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>551302</t>
+          <t>600102</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>502988</t>
+          <t>548457</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>502988</t>
+          <t>548457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>502988</t>
+          <t>548457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>446095</t>
+          <t>486999</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>446095</t>
+          <t>486999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>446095</t>
+          <t>486999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>949083</t>
+          <t>1035456</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>949083</t>
+          <t>1035456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>949083</t>
+          <t>1035456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>50827</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59353</t>
+          <t>67051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37568</t>
+          <t>45950</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>34997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49537</t>
+          <t>59085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>82113</t>
+          <t>96777</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65199</t>
+          <t>79674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102741</t>
+          <t>118861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>17125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34324</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149240</t>
+          <t>155534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127359</t>
+          <t>134437</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171116</t>
+          <t>177924</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>144355</t>
+          <t>155064</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127699</t>
+          <t>137215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161374</t>
+          <t>172574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>293595</t>
+          <t>310598</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>269678</t>
+          <t>281206</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>322007</t>
+          <t>337396</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>242310</t>
+          <t>259127</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221142</t>
+          <t>236073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265579</t>
+          <t>282570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>175884</t>
+          <t>196180</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160645</t>
+          <t>179032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194271</t>
+          <t>215100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>418193</t>
+          <t>455307</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>390269</t>
+          <t>427260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446918</t>
+          <t>484502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>450094</t>
+          <t>480984</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450094</t>
+          <t>480984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>450094</t>
+          <t>480984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>380873</t>
+          <t>421374</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>380873</t>
+          <t>421374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380873</t>
+          <t>421374</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>830967</t>
+          <t>902358</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830967</t>
+          <t>902358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830967</t>
+          <t>902358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>60970</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>46461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75696</t>
+          <t>79248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>52951</t>
+          <t>75838</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>60100</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81178</t>
+          <t>95745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45733</t>
+          <t>38214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12516</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>52463</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>102101</t>
+          <t>108523</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>89267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>129154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49056</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>141743</t>
+          <t>152550</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58067</t>
+          <t>129406</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210907</t>
+          <t>173628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>488223</t>
+          <t>266267</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>374792</t>
+          <t>243487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>596928</t>
+          <t>288248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>106224</t>
+          <t>116771</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97075</t>
+          <t>105298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116546</t>
+          <t>127671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>594447</t>
+          <t>383039</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>485584</t>
+          <t>359452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>737575</t>
+          <t>411407</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>667290</t>
+          <t>470669</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>667290</t>
+          <t>470669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>667290</t>
+          <t>470669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>833545</t>
+          <t>657460</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>833545</t>
+          <t>657460</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>833545</t>
+          <t>657460</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24626</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>17379</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>42541</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59865</t>
+          <t>60532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>115668</t>
+          <t>162431</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89480</t>
+          <t>136493</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>147082</t>
+          <t>194703</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>83563</t>
+          <t>119158</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>101351</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>111574</t>
+          <t>137363</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>199231</t>
+          <t>281589</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>140645</t>
+          <t>249761</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>241251</t>
+          <t>312415</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>58802</t>
+          <t>55967</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42414</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80227</t>
+          <t>76007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36618</t>
+          <t>37182</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52854</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>95420</t>
+          <t>93149</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>72865</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>121083</t>
+          <t>115775</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>243294</t>
+          <t>255718</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>227839</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>272313</t>
+          <t>289861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>227685</t>
+          <t>245617</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>121926</t>
+          <t>223142</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>298101</t>
+          <t>269136</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>470979</t>
+          <t>501335</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>329814</t>
+          <t>460746</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>537833</t>
+          <t>541312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>582803</t>
+          <t>621097</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>545895</t>
+          <t>583902</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>621181</t>
+          <t>653616</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>605491</t>
+          <t>430670</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>493938</t>
+          <t>404068</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>780801</t>
+          <t>457757</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1188294</t>
+          <t>1051766</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1078121</t>
+          <t>1005508</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1461740</t>
+          <t>1097127</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1033291</t>
+          <t>1130192</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1033291</t>
+          <t>1130192</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1033291</t>
+          <t>1130192</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>973734</t>
+          <t>856682</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>973734</t>
+          <t>856682</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>973734</t>
+          <t>856682</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2007025</t>
+          <t>1986874</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2007025</t>
+          <t>1986874</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2007025</t>
+          <t>1986874</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>35248</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>33121</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>29334</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>42125</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>62205</t>
+          <t>125023</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>104136</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>76844</t>
+          <t>150311</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>157230</t>
+          <t>119819</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>89001</t>
+          <t>102142</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>342288</t>
+          <t>138667</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>219435</t>
+          <t>244842</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>150909</t>
+          <t>216972</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>402756</t>
+          <t>276994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>42610</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58950</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>39279</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>30113</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>51843</t>
+          <t>51304</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>80830</t>
+          <t>81128</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>62245</t>
+          <t>65928</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>103488</t>
+          <t>99760</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>90317</t>
+          <t>92279</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>72472</t>
+          <t>73536</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>114621</t>
+          <t>113935</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>152577</t>
+          <t>168836</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>112507</t>
+          <t>149387</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>177441</t>
+          <t>191360</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>242894</t>
+          <t>261115</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>198279</t>
+          <t>234916</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>278120</t>
+          <t>290421</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>254857</t>
+          <t>275139</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>227204</t>
+          <t>248941</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>277301</t>
+          <t>301032</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>472401</t>
+          <t>476790</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>351082</t>
+          <t>451119</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>530039</t>
+          <t>501893</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>727258</t>
+          <t>751929</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>599028</t>
+          <t>716306</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>783283</t>
+          <t>787125</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>839515</t>
+          <t>828502</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>839515</t>
+          <t>828502</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>839515</t>
+          <t>828502</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1314561</t>
+          <t>1396465</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1314561</t>
+          <t>1396465</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1314561</t>
+          <t>1396465</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>32897</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>40531</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>65543</t>
+          <t>91128</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>48670</t>
+          <t>68910</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>80701</t>
+          <t>113032</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>89936</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>107397</t>
+          <t>139562</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>32238</t>
+          <t>30320</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>52703</t>
+          <t>45968</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>57994</t>
+          <t>56872</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>81869</t>
+          <t>77199</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>113453</t>
+          <t>125535</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>95227</t>
+          <t>106196</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>135852</t>
+          <t>152099</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>171447</t>
+          <t>182406</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>143907</t>
+          <t>156614</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>205016</t>
+          <t>213682</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>127199</t>
+          <t>122694</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>103800</t>
+          <t>101687</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>150677</t>
+          <t>147487</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>546356</t>
+          <t>589160</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>516820</t>
+          <t>558202</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>569173</t>
+          <t>617985</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>673555</t>
+          <t>711854</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>639138</t>
+          <t>671669</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>709455</t>
+          <t>742536</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>224666</t>
+          <t>222942</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>224666</t>
+          <t>222942</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>224666</t>
+          <t>222942</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>759216</t>
+          <t>842019</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>759216</t>
+          <t>842019</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>759216</t>
+          <t>842019</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>983882</t>
+          <t>1064961</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>983882</t>
+          <t>1064961</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>983882</t>
+          <t>1064961</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,102 +5495,102 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31487</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>55903</t>
+          <t>61471</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>27997</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>40351</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>66482</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>48613</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>91706</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>22737</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>14852</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>37098</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>54224</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>37362</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>78124</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>63071</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>39832</t>
+          <t>47804</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>83655</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>50149</t>
+          <t>55216</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>37762</t>
+          <t>43531</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>65782</t>
+          <t>72108</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>105863</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>84330</t>
+          <t>98590</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>131403</t>
+          <t>141801</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>328274</t>
+          <t>486569</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>252064</t>
+          <t>441765</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>375562</t>
+          <t>536055</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>387837</t>
+          <t>437235</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>307378</t>
+          <t>401693</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>592783</t>
+          <t>477663</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>716111</t>
+          <t>923804</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>615623</t>
+          <t>866930</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>957653</t>
+          <t>989044</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>170309</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>130966</t>
+          <t>135414</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>208490</t>
+          <t>194829</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>132040</t>
+          <t>134978</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>103793</t>
+          <t>116690</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>153264</t>
+          <t>158277</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>302348</t>
+          <t>297942</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>255530</t>
+          <t>261157</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>346268</t>
+          <t>336776</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>796553</t>
+          <t>826182</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>626977</t>
+          <t>769602</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>888551</t>
+          <t>878545</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>821220</t>
+          <t>890418</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>661904</t>
+          <t>843341</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>894477</t>
+          <t>937940</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1617773</t>
+          <t>1716600</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1397664</t>
+          <t>1640345</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1744860</t>
+          <t>1795220</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1971039</t>
+          <t>1843936</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1839584</t>
+          <t>1781431</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2291789</t>
+          <t>1904776</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2151705</t>
+          <t>2076522</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2008238</t>
+          <t>2025288</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2384177</t>
+          <t>2132998</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>4122744</t>
+          <t>3920458</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3915515</t>
+          <t>3837295</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4479297</t>
+          <t>4006021</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3353376</t>
+          <t>3421207</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3353376</t>
+          <t>3421207</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3353376</t>
+          <t>3421207</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3565688</t>
+          <t>3622366</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3565688</t>
+          <t>3622366</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3565688</t>
+          <t>3622366</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>6919063</t>
+          <t>7043573</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6919063</t>
+          <t>7043573</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6919063</t>
+          <t>7043573</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
